--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_973_Korea_North_Yellow_Sea.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_973_Korea_North_Yellow_Sea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R151a19377e4e41b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R8cd7e1b7d7074b1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rc4ebfb2cc4014f20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rf11709cebe15489d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R6cb98c0b8ec54475"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rde803f4e56044b7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R32e29bfc82ef4074"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R197f0b8c8f914bee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R399c3d52b771498c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R4a919dff557a48c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R4183affc44fd412d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Re933bb9845064f4f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ973CommercialTable" displayName="EEZ973CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ973CommercialTable" displayName="EEZ973CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ973FunctionalTable" displayName="EEZ973FunctionalTable" ref="A1:O19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O19"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ973FunctionalTable" displayName="EEZ973FunctionalTable" ref="A1:E19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E19"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ973ValidationTable" displayName="EEZ973ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ973ValidationTable" displayName="EEZ973ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -4580,7 +4534,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73ddb0345b97403d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re81b10b3eeb54a73"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4590,20 +4544,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4611,606 +4555,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2032.4354173112</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.14</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>138.03842646028852</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2032.4354173112</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>138.03842646028852</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$59,A2,'Species'!$U$2:$U$59))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>280554.1868877979</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.14</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>138.03842646028852</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>280554.1868877979</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>482.9157456254</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.16</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1445.439770745928</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>482.9157456254</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1445.439770745928</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$59,A3,'Species'!$U$2:$U$59))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>698025.624646377</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.16</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1445.439770745928</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>698025.624646377</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>16746.945985377002</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.9740615861928257</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>94.20231729551102</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>16746.945985377002</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>171.72585189758706</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$59,A4,'Species'!$U$2:$U$59))</x:f>
-        <x:v>2875883.5660217414</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.9740615861928257</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>94.20231729551102</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1577601.1194452688</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1298282.4465764726</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.8229472143332321</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.8229472143332321</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1940.6920436587</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.581505002865157</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>381.5091890579015</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1940.6920436587</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>397.8898596382963</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$59,A5,'Species'!$U$2:$U$59))</x:f>
-        <x:v>772181.6848525185</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.581505002865157</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>381.5091890579015</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>740391.8477873522</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>31789.837065166328</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.042936503366656</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.04293650336665603</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>4534.427333081301</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.946049208335856</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>88.3179964674706</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>4534.427333081301</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>98.42667874560381</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$59,A6,'Species'!$U$2:$U$59))</x:f>
-        <x:v>446308.6224084783</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.946049208335856</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>88.3179964674706</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>400471.5371850765</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>45837.08522340178</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1144577853037738</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.11445778530377387</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1083.1836227341998</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.169790734712909</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>14.783958498016775</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1083.1836227341998</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>24.402805662308968</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$59,A7,'Species'!$U$2:$U$59))</x:f>
-        <x:v>26432.719442178473</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.169790734712909</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>14.783958498016775</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>16013.74172423387</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>10418.977717944603</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.6506273110535674</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.6506273110535675</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>39335.86897466821</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.748065474363922</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>559.8419970774621</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>39335.86897466821</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>985.8090759665978</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$59,A8,'Species'!$U$2:$U$59))</x:f>
-        <x:v>38777656.64626083</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.748065474363922</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>559.8419970774621</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>22021871.44355563</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>16755785.202705197</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.7608701760725483</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.7608701760725484</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>22236.1687226481</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.557863086270141</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>361.2959441454794</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>22236.1687226481</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>666.4281510840846</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$59,A9,'Species'!$U$2:$U$59))</x:f>
-        <x:v>14818808.809028124</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.557863086270141</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>361.2959441454794</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>8033837.572827324</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>6784971.2362008</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.8445492175681348</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.8445492175681348</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>652.8426201031999</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.611203674036248</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>408.5109235614953</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>652.8426201031999</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>410.9906781475042</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$59,A10,'Species'!$U$2:$U$59))</x:f>
-        <x:v>268312.2311598076</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.611203674036248</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>408.5109235614953</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>266693.3416786646</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1618.8894811429782</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0060702283414842</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.006070228341484271</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1.475e-7</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.35</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2238.7211385683377</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1.475e-7</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$59,A11,'Species'!$U$2:$U$59))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>0.0003302113679388298</x:v>
       </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.35</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>0.0003302113679388298</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf46f9d06c160490f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8b9fe454e2a49dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5220,20 +4770,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5241,1038 +4781,364 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>20912.6951468415</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.160966062564673</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1448.6586453827656</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>20912.6951468415</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1576.0402690631392</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$59,A2,'Species'!$U$2:$U$59))</x:f>
-        <x:v>32959249.686063483</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.160966062564673</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1448.6586453827656</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>30295356.622726142</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>2663893.063337341</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0879307379183982</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.08793073791839817</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>3649.7262930125003</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.324914548213565</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2113.073230621501</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>3649.7262930125003</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2521.150590266265</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$59,A3,'Species'!$U$2:$U$59))</x:f>
-        <x:v>9201509.597938772</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.324914548213565</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2113.073230621501</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>7712138.928860159</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1489370.6690786136</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.19312031108583</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.19312031108583</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1602.5063150965</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.31370293580953</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2059.22089226273</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1602.5063150965</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2111.5276156110917</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$59,A4,'Species'!$U$2:$U$59))</x:f>
-        <x:v>3383736.3385174293</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.31370293580953</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2059.22089226273</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>3299914.4840296744</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>83821.85448775487</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.025401220211439</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.025401220211439</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>38.4959784874</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.25</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1778.2794100389228</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>38.4959784874</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1778.2794100389228</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$59,A5,'Species'!$U$2:$U$59))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>68456.60591344474</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.25</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1778.2794100389228</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>68456.60591344474</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>196.1396377177</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.35</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2238.7211385683377</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>196.1396377177</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$59,A6,'Species'!$U$2:$U$59))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>439101.9530697506</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.35</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>439101.9530697506</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>148.5431927355</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.5751554719927467</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>375.97197346413844</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>148.5431927355</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>394.0699776756683</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$59,A7,'Species'!$U$2:$U$59))</x:f>
-        <x:v>58536.41264515099</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.5751554719927467</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>375.97197346413844</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>55848.077317429816</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2688.335327721172</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0481365779602614</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.04813657796026149</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1.475e-7</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.35</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2238.7211385683377</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1.475e-7</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$59,A8,'Species'!$U$2:$U$59))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>0.0003302113679388298</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.35</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>0.0003302113679388298</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>5391.3076529345</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.372360601970858</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>235.7005532739654</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>5391.3076529345</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>371.18996027952795</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$59,A9,'Species'!$U$2:$U$59))</x:f>
-        <x:v>2001199.273547472</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.372360601970858</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>235.7005532739654</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1270734.1966668253</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>730465.0768806466</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.5748370342095765</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.5748370342095765</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>4816.6388969156</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.4822570359423874</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>303.5687315447393</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>4816.6388969156</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>314.7340652778319</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$59,A10,'Species'!$U$2:$U$59))</x:f>
-        <x:v>1515960.3410015786</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.4822570359423874</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>303.5687315447393</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1462180.960245721</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>53779.380755857565</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0367802496531071</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.03678024965310715</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>17140.6796863729</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.3327066369974556</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>215.13280361738802</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>17140.6796863729</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>231.0517759706516</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$59,A11,'Species'!$U$2:$U$59))</x:f>
-        <x:v>3960384.48288053</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.3327066369974556</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>215.13280361738802</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>3687522.476837013</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>272862.00604351703</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0739960251788256</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.07399602517882563</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>13075.714263264403</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.2420536383549825</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>174.6037787277591</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>13075.714263264403</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>201.86648491713498</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$59,A12,'Species'!$U$2:$U$59))</x:f>
-        <x:v>2639548.4761060304</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.2420536383549825</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>174.6037787277591</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>2283069.1199304215</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>356479.35617560893</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1561404133863775</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.15614041338637744</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>873.1091723948</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.405059842460863</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>254.1322856294301</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>873.1091723948</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>385.3892379093855</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$59,A13,'Species'!$U$2:$U$59))</x:f>
-        <x:v>336486.87856092624</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.405059842460863</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>254.1322856294301</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>221885.22958471064</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>114601.6489762156</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.516490661368982</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.5164906613689819</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>2482.0162711586</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.2858066679864666</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>19.311084668094743</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>2482.0162711586</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>25.184063610301198</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$59,A14,'Species'!$U$2:$U$59))</x:f>
-        <x:v>62507.25565466077</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.2858066679864666</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>19.311084668094743</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>47930.42635993252</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>14576.829294728246</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.3041247575238295</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.30412475752382956</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>11355.6383324425</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.7849614696643252</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>60.94828219054605</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>11355.6383324425</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>77.02643099995002</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$59,A15,'Species'!$U$2:$U$59))</x:f>
-        <x:v>874684.2924742699</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.7849614696643252</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>60.94828219054605</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>692106.6495394873</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>182577.64293478255</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.2637998682085567</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.2637998682085568</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small bathydemersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>615.9356551874</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.51</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>323.5936569296281</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>615.9356551874</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$59,A16,'Species'!$U$2:$U$59))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>199312.8710954372</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.51</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>199312.8710954372</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>2734.7105311883</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.0000197170895806</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>100.00454013071537</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>2734.7105311883</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>100.01163328715025</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$59,A17,'Species'!$U$2:$U$59))</x:f>
-        <x:v>273502.8667917121</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.0000197170895806</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>100.00454013071537</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>273483.4690621103</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>19.39772960182745</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0000709283441092</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.00007092834410924512</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>2109.4273742859</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.130145274193094</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>134.94141945069768</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>2109.4273742859</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>135.70587117511923</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$59,A18,'Species'!$U$2:$U$59))</x:f>
-        <x:v>286261.6795081124</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.130145274193094</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>134.94141945069768</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>284649.1241142975</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>1612.555393814866</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0056650636071072</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.005665063607107265</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>1902.1960651713</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.5679762349847963</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>369.8079429773242</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>1902.1960651713</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>369.9540188438465</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$59,A19,'Species'!$U$2:$U$59))</x:f>
-        <x:v>703725.0789390737</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.5679762349847963</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>369.8079429773242</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>703447.2140005586</x:v>
       </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>277.86493851512205</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0003950046755248</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.0003950046755248097</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G19">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O19">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R554862e61f07413e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82ecb429f7f04ad3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6447,7 +5313,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6546,7 +5412,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>58964164.09103805</x:v>
+        <x:v>34035460.416067936</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6560,7 +5426,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>58964164.09103804</x:v>
+        <x:v>52997138.40968333</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6574,7 +5440,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>1.4901161193847656e-8</x:v>
+        <x:v>-24928703.674970098</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6588,7 +5454,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>7.450580596923828e-9</x:v>
+        <x:v>-5967025.6813547015</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6599,9 +5465,9 @@
         <x:v>EEZ_973</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6613,47 +5479,19 @@
         <x:v>EEZ_973</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_973</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_973</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3e0ff3432b24361"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17bd759b447745ad"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6700,7 +5538,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
